--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -1345,7 +1345,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -630,16 +630,16 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam</t>
-  </si>
-  <si>
-    <t>physicalExam</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.id</t>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -661,7 +661,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -680,7 +680,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -711,19 +711,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -753,7 +753,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -777,7 +777,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -804,7 +804,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -828,7 +828,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -859,7 +859,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:physicalExam.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1408,7 +1408,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="566">
   <si>
     <t>Property</t>
   </si>
@@ -614,29 +614,41 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:first</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -3872,22 +3884,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3914,10 +3928,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3925,13 +3939,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3941,7 +3955,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3956,13 +3970,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -3994,7 +4008,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4036,10 +4050,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4047,10 +4061,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4073,13 +4087,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4130,7 +4144,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4154,7 +4168,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4165,10 +4179,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4197,7 +4211,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4238,19 +4252,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4274,7 +4288,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4285,10 +4299,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4311,19 +4325,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4372,7 +4386,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4393,10 +4407,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4407,10 +4421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4433,13 +4447,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4490,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4514,7 +4528,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4525,10 +4539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4557,7 +4571,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4598,19 +4612,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4634,7 +4648,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4645,10 +4659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4656,7 +4670,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4674,23 +4688,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4732,7 +4746,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4753,10 +4767,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4767,10 +4781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4793,16 +4807,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4852,7 +4866,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4873,10 +4887,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4887,10 +4901,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4916,21 +4930,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4972,7 +4986,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4993,10 +5007,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5007,10 +5021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5033,17 +5047,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5092,7 +5106,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5113,10 +5127,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5127,10 +5141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5153,19 +5167,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5214,7 +5228,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5235,10 +5249,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5249,10 +5263,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5275,19 +5289,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5336,7 +5350,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5357,10 +5371,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5371,14 +5385,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5400,16 +5414,16 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5438,7 +5452,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5456,7 +5470,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>94</v>
@@ -5471,30 +5485,30 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5517,13 +5531,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5574,7 +5588,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5598,7 +5612,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5609,10 +5623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5641,7 +5655,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5682,19 +5696,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5718,7 +5732,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5729,10 +5743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5755,19 +5769,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5804,17 +5818,17 @@
         <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5835,10 +5849,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5849,13 +5863,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>83</v>
@@ -5877,19 +5891,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5918,7 +5932,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>83</v>
@@ -5936,7 +5950,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5957,10 +5971,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5971,10 +5985,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5997,13 +6011,13 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6054,7 +6068,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6078,7 +6092,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6089,10 +6103,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6121,7 +6135,7 @@
         <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>143</v>
@@ -6162,19 +6176,19 @@
         <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6198,7 +6212,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6209,10 +6223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6238,23 +6252,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6296,7 +6310,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6317,10 +6331,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6331,10 +6345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6357,16 +6371,16 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6416,7 +6430,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6437,10 +6451,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6451,10 +6465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6480,21 +6494,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6536,7 +6550,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6557,10 +6571,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6571,10 +6585,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6597,17 +6611,17 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6617,7 +6631,7 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>83</v>
@@ -6656,7 +6670,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6677,10 +6691,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6691,10 +6705,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6717,19 +6731,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6778,7 +6792,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6799,10 +6813,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6813,10 +6827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6839,19 +6853,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6900,7 +6914,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6921,10 +6935,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6935,10 +6949,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6961,19 +6975,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7022,7 +7036,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7037,19 +7051,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7057,10 +7071,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7083,16 +7097,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7142,7 +7156,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7163,13 +7177,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7177,14 +7191,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7203,19 +7217,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7264,7 +7278,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7279,19 +7293,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7299,14 +7313,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7325,19 +7339,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7386,7 +7400,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7401,19 +7415,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7421,10 +7435,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7447,16 +7461,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7506,7 +7520,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7527,13 +7541,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7541,10 +7555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7567,19 +7581,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7628,7 +7642,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7643,19 +7657,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7663,10 +7677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7689,19 +7703,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7738,17 +7752,17 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7757,7 +7771,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7766,30 +7780,30 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>83</v>
@@ -7814,16 +7828,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7852,7 +7866,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7870,7 +7884,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7879,7 +7893,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7888,27 +7902,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7934,16 +7948,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7968,31 +7982,31 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8001,7 +8015,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8016,7 +8030,7 @@
         <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8027,14 +8041,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8056,16 +8070,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8090,13 +8104,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8114,7 +8128,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8132,27 +8146,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8175,19 +8189,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8236,7 +8250,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8257,10 +8271,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8271,10 +8285,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8300,13 +8314,13 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8336,7 +8350,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8354,7 +8368,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8372,27 +8386,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8418,16 +8432,16 @@
         <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8456,25 +8470,25 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8495,10 +8509,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8509,10 +8523,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8535,16 +8549,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8594,7 +8608,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8612,27 +8626,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8655,16 +8669,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8714,7 +8728,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8732,27 +8746,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8775,19 +8789,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8836,7 +8850,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8848,7 +8862,7 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8857,10 +8871,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8871,10 +8885,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8897,13 +8911,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8954,7 +8968,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8978,7 +8992,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8989,10 +9003,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9021,7 +9035,7 @@
         <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9074,7 +9088,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9098,7 +9112,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9109,14 +9123,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9138,10 +9152,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9196,7 +9210,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9231,10 +9245,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9257,13 +9271,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9314,7 +9328,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9323,7 +9337,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9335,10 +9349,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9349,10 +9363,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9375,13 +9389,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9432,7 +9446,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9441,7 +9455,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9453,10 +9467,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9481,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9496,16 +9510,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9533,10 +9547,10 @@
         <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9554,7 +9568,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9572,13 +9586,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9589,10 +9603,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9618,16 +9632,16 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9652,13 +9666,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9676,7 +9690,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9694,13 +9708,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9711,10 +9725,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9737,17 +9751,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9796,7 +9810,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9820,7 +9834,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9831,10 +9845,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9857,13 +9871,13 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9914,7 +9928,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9935,10 +9949,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9949,10 +9963,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9975,16 +9989,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10034,7 +10048,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10055,10 +10069,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10069,10 +10083,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10095,16 +10109,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10154,7 +10168,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10175,10 +10189,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10189,10 +10203,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10215,19 +10229,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10276,7 +10290,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10297,10 +10311,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10311,10 +10325,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10337,13 +10351,13 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10394,7 +10408,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10418,7 +10432,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10429,10 +10443,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10461,7 +10475,7 @@
         <v>141</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10514,7 +10528,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10538,7 +10552,7 @@
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10549,14 +10563,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10578,10 +10592,10 @@
         <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>143</v>
@@ -10636,7 +10650,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10671,10 +10685,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10700,16 +10714,16 @@
         <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10738,7 +10752,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10756,7 +10770,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10774,16 +10788,16 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -10791,10 +10805,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10817,13 +10831,13 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10874,7 +10888,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10898,7 +10912,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10909,10 +10923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10941,7 +10955,7 @@
         <v>141</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -10982,19 +10996,19 @@
         <v>83</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11018,7 +11032,7 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11029,10 +11043,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11055,19 +11069,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11104,17 +11118,17 @@
         <v>83</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11135,10 +11149,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11149,13 +11163,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -11177,19 +11191,19 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11218,7 +11232,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11236,7 +11250,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11257,10 +11271,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11271,10 +11285,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11297,13 +11311,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11354,7 +11368,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11378,7 +11392,7 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11389,10 +11403,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11421,7 +11435,7 @@
         <v>141</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>143</v>
@@ -11462,19 +11476,19 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11498,7 +11512,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11509,10 +11523,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11538,23 +11552,23 @@
         <v>108</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>83</v>
@@ -11596,7 +11610,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11617,10 +11631,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11631,10 +11645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11657,16 +11671,16 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11716,7 +11730,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11737,10 +11751,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11751,10 +11765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11780,21 +11794,21 @@
         <v>114</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>83</v>
@@ -11836,7 +11850,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11857,10 +11871,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11871,10 +11885,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11897,17 +11911,17 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -11917,7 +11931,7 @@
         <v>83</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>83</v>
@@ -11956,7 +11970,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11977,10 +11991,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11991,10 +12005,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12017,19 +12031,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12078,7 +12092,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12099,10 +12113,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12113,10 +12127,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12139,19 +12153,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12200,7 +12214,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12221,10 +12235,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12235,10 +12249,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12261,19 +12275,19 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12322,7 +12336,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12340,27 +12354,27 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12386,16 +12400,16 @@
         <v>188</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12420,13 +12434,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12444,7 +12458,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12453,7 +12467,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -12468,7 +12482,7 @@
         <v>137</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12479,14 +12493,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12508,16 +12522,16 @@
         <v>188</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12542,13 +12556,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -12566,7 +12580,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12584,27 +12598,27 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12630,16 +12644,16 @@
         <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12688,7 +12702,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12709,10 +12723,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1239,7 +1239,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1421,7 +1421,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1746,7 +1746,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -1492,7 +1492,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -2084,15 +2084,15 @@
   <dimension ref="A1:AP88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.38671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.05859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2103,28 +2103,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.21875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.34375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -1318,7 +1318,13 @@
     <t>ICD-11</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationPhysicalExamBodySite_VS</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1535,9 +1541,6 @@
   </si>
   <si>
     <t>適切な解釈のためにターゲット母集団を特定できる必要があります。 / Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
@@ -2109,7 +2112,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -8346,11 +8349,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8386,27 +8391,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8432,16 +8437,16 @@
         <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8470,7 +8475,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8488,7 +8493,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8509,10 +8514,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8523,10 +8528,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8549,16 +8554,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8608,7 +8613,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8626,27 +8631,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8669,16 +8674,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8728,7 +8733,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8746,27 +8751,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8789,19 +8794,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8850,7 +8855,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8862,7 +8867,7 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8871,10 +8876,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8885,10 +8890,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9003,10 +9008,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9123,14 +9128,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9152,10 +9157,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9210,7 +9215,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9245,10 +9250,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9271,13 +9276,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9328,7 +9333,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9337,7 +9342,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9349,10 +9354,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9363,10 +9368,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9389,13 +9394,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9446,7 +9451,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9455,7 +9460,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9467,10 +9472,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9481,10 +9486,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9510,16 +9515,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9547,10 +9552,10 @@
         <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9568,7 +9573,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9586,10 +9591,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>407</v>
@@ -9603,10 +9608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9632,16 +9637,16 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9666,13 +9671,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9690,7 +9695,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9708,10 +9713,10 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>407</v>
@@ -9725,10 +9730,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9751,17 +9756,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9810,7 +9815,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9834,7 +9839,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9845,10 +9850,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9874,10 +9879,10 @@
         <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9928,7 +9933,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9949,10 +9954,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9963,10 +9968,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9989,16 +9994,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10048,7 +10053,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10069,10 +10074,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10083,10 +10088,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10109,16 +10114,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10168,7 +10173,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10189,10 +10194,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10203,10 +10208,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10229,19 +10234,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10290,7 +10295,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10311,10 +10316,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10330,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10443,10 +10448,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,14 +10568,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10592,10 +10597,10 @@
         <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>143</v>
@@ -10650,7 +10655,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10685,10 +10690,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10714,13 +10719,13 @@
         <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>289</v>
@@ -10770,7 +10775,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10788,7 +10793,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>293</v>
@@ -10805,10 +10810,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10923,10 +10928,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11043,10 +11048,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11163,10 +11168,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>302</v>
@@ -11285,10 +11290,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11403,10 +11408,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11523,10 +11528,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11645,10 +11650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11765,10 +11770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11808,7 +11813,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>83</v>
@@ -11885,10 +11890,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11931,7 +11936,7 @@
         <v>83</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>83</v>
@@ -12005,10 +12010,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12127,10 +12132,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12249,10 +12254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12278,13 +12283,13 @@
         <v>375</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>378</v>
@@ -12336,7 +12341,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12354,7 +12359,7 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>382</v>
@@ -12371,10 +12376,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12400,13 +12405,13 @@
         <v>188</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>392</v>
@@ -12458,7 +12463,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12493,10 +12498,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12522,16 +12527,16 @@
         <v>188</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12580,7 +12585,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12615,10 +12620,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12644,16 +12649,16 @@
         <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12702,7 +12707,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12723,10 +12728,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1048,7 +1048,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1242,7 +1242,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1271,7 +1271,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1324,7 +1324,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1388,7 +1388,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1513,7 +1513,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1546,7 +1546,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -620,7 +620,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -1395,7 +1395,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -944,10 +944,6 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
     <t>Observation.code.coding:physicalExamCode</t>
   </si>
   <si>
@@ -963,6 +959,12 @@
     <t>推奨項目コードは必須ではない、派生先によるコード体系を作成し割り振ることを否定しない</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS"/&gt;
+  &lt;code value="physical-findings"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:physicalExamCode.id</t>
   </si>
   <si>
@@ -981,9 +983,6 @@
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS</t>
-  </si>
-  <si>
     <t>Observation.code.coding:physicalExamCode.version</t>
   </si>
   <si>
@@ -994,9 +993,6 @@
   </si>
   <si>
     <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>physical-findings</t>
   </si>
   <si>
     <t>Observation.code.coding:physicalExamCode.display</t>
@@ -1670,6 +1666,10 @@
     <t>Observation.component.code.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>Observation.component.code.coding:physicalExamCode</t>
   </si>
   <si>
@@ -1689,6 +1689,9 @@
   </si>
   <si>
     <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_PhysicalExamCode_CS</t>
   </si>
   <si>
     <t>Observation.component.code.coding:physicalExamCode.version</t>
@@ -5821,7 +5824,7 @@
         <v>83</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -5866,13 +5869,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>299</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>83</v>
@@ -5897,13 +5900,13 @@
         <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>223</v>
@@ -5916,7 +5919,7 @@
         <v>83</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>83</v>
@@ -6237,7 +6240,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
@@ -6271,7 +6274,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6348,10 +6351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6468,10 +6471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6511,7 +6514,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6588,10 +6591,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6634,7 +6637,7 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>83</v>
@@ -6708,10 +6711,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6830,10 +6833,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6952,10 +6955,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6978,19 +6981,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7039,7 +7042,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7054,19 +7057,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7074,10 +7077,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7100,16 +7103,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7159,7 +7162,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7183,10 +7186,10 @@
         <v>293</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7194,14 +7197,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7220,19 +7223,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7281,7 +7284,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7296,19 +7299,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7316,14 +7319,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7342,19 +7345,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7403,7 +7406,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7418,19 +7421,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7438,10 +7441,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7464,16 +7467,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7523,7 +7526,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7544,13 +7547,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7558,10 +7561,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7584,19 +7587,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7645,7 +7648,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7660,19 +7663,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7680,10 +7683,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7706,19 +7709,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7755,7 +7758,7 @@
         <v>83</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7765,7 +7768,7 @@
         <v>195</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7774,7 +7777,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7783,30 +7786,30 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>83</v>
@@ -7831,16 +7834,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7869,7 +7872,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7887,7 +7890,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7896,7 +7899,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7905,27 +7908,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7951,16 +7954,16 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7985,14 +7988,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="Y49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8009,7 +8012,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8018,7 +8021,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8033,7 +8036,7 @@
         <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8044,14 +8047,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8073,16 +8076,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8107,13 +8110,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8131,7 +8134,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8149,27 +8152,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8192,19 +8195,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8253,7 +8256,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8274,10 +8277,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8288,10 +8291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8317,13 +8320,13 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8349,14 +8352,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8373,7 +8376,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8391,27 +8394,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8437,16 +8440,16 @@
         <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8475,7 +8478,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8493,7 +8496,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8514,10 +8517,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8528,10 +8531,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8554,16 +8557,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8613,7 +8616,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8631,27 +8634,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>440</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8674,16 +8677,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8733,7 +8736,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8751,27 +8754,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8794,19 +8797,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8855,7 +8858,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8867,19 +8870,19 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8890,10 +8893,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9008,10 +9011,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9128,14 +9131,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9157,10 +9160,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9215,7 +9218,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9250,10 +9253,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9276,13 +9279,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9333,7 +9336,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9342,7 +9345,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9354,10 +9357,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9368,10 +9371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9394,13 +9397,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9451,7 +9454,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9460,7 +9463,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9472,10 +9475,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9486,10 +9489,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9515,16 +9518,16 @@
         <v>188</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9552,10 +9555,10 @@
         <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9573,7 +9576,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9591,13 +9594,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9608,10 +9611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9637,16 +9640,16 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9671,13 +9674,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9695,7 +9698,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9713,13 +9716,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9730,10 +9733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9756,17 +9759,17 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9815,7 +9818,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9839,7 +9842,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9850,10 +9853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9879,10 +9882,10 @@
         <v>206</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9933,7 +9936,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9954,10 +9957,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9968,10 +9971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9994,16 +9997,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10053,7 +10056,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10074,10 +10077,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10088,10 +10091,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10114,16 +10117,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10173,7 +10176,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10194,10 +10197,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10208,10 +10211,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10234,19 +10237,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10295,7 +10298,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10316,10 +10319,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10330,10 +10333,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10448,10 +10451,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10568,14 +10571,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10597,10 +10600,10 @@
         <v>140</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>143</v>
@@ -10655,7 +10658,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10690,10 +10693,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10719,13 +10722,13 @@
         <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>289</v>
@@ -10775,7 +10778,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>94</v>
@@ -10793,7 +10796,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>293</v>
@@ -10810,10 +10813,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10928,10 +10931,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11048,10 +11051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11123,7 +11126,7 @@
         <v>83</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>300</v>
+        <v>528</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11168,13 +11171,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -11199,13 +11202,13 @@
         <v>219</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>223</v>
@@ -11290,10 +11293,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11408,10 +11411,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11528,10 +11531,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11573,7 +11576,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>312</v>
+        <v>536</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>83</v>
@@ -12280,7 +12283,7 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>549</v>
@@ -12292,7 +12295,7 @@
         <v>551</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12362,16 +12365,16 @@
         <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="86">
@@ -12414,7 +12417,7 @@
         <v>556</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12439,13 +12442,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12472,7 +12475,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -12487,7 +12490,7 @@
         <v>137</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12505,7 +12508,7 @@
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12561,13 +12564,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -12603,19 +12606,19 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="88">
@@ -12728,10 +12731,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1623,7 +1623,7 @@
     <t>【JP Core仕様】具体的な所見を記載する</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
